--- a/Resource Links/Tech-Bootcamp-Links.xlsx
+++ b/Resource Links/Tech-Bootcamp-Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Resource Links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC061C2-508F-4F40-B45F-539047152140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D77390-4543-4788-928B-E5E18CCC866C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>Serial No.</t>
   </si>
@@ -59,30 +59,6 @@
     <t>TechBootrcamp-Steve</t>
   </si>
   <si>
-    <t>Capstone Projects</t>
-  </si>
-  <si>
-    <t>User Stories, Team Assignments, Deliverables etc.</t>
-  </si>
-  <si>
-    <t>MayJune.xlsx</t>
-  </si>
-  <si>
-    <t>GitHub Organization for Capstone Project (ECommerce Shopping Site)</t>
-  </si>
-  <si>
-    <t>GitHub Organization and Repositories for ECommerce Shopping Site Capstone Project</t>
-  </si>
-  <si>
-    <t>CAPSTONE-PROJECT-TECH-BOOTCAMP</t>
-  </si>
-  <si>
-    <t>GitHub Repository for Capstone Project (Resource Upskilling Portal)</t>
-  </si>
-  <si>
-    <t>https://github.com/Mmind007/MCQ.git</t>
-  </si>
-  <si>
     <t>GitHub Repostory for Tech Bootcamp</t>
   </si>
   <si>
@@ -99,6 +75,15 @@
   </si>
   <si>
     <t>Attendance/Assignment and Demos Status</t>
+  </si>
+  <si>
+    <t>Recordings</t>
+  </si>
+  <si>
+    <t>Spring Boot  Recordings</t>
+  </si>
+  <si>
+    <t>Spring Core, REST and Data JPA Recordings</t>
   </si>
 </sst>
 </file>
@@ -174,7 +159,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -201,7 +186,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -540,11 +524,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" customWidth="1"/>
     <col min="3" max="3" width="43.7109375" customWidth="1"/>
     <col min="4" max="4" width="43.5703125" customWidth="1"/>
   </cols>
@@ -568,13 +552,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -588,13 +572,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -616,122 +600,50 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D11" s="10"/>
-    </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>6</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D13" s="10"/>
-    </row>
-    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D15" s="10"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D16" s="10"/>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D18" s="10"/>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D19" s="10"/>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D20" s="10"/>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D22" s="10"/>
-    </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D23" s="10"/>
-    </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D24" s="10"/>
-    </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D25" s="10"/>
-    </row>
-    <row r="26" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D26" s="10"/>
-    </row>
-    <row r="27" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D27" s="10"/>
+      <c r="C10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="10"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D6" r:id="rId1" xr:uid="{0C8BF935-1079-4255-9D07-C93C89C0D00D}"/>
-    <hyperlink ref="D8" r:id="rId2" xr:uid="{418A416B-CE9C-4292-A99D-A142A3F5E6ED}"/>
-    <hyperlink ref="D10" r:id="rId3" xr:uid="{E00CA03C-062C-44AF-A5CA-5532C5548383}"/>
-    <hyperlink ref="D14" r:id="rId4" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
-    <hyperlink ref="D12" r:id="rId5" xr:uid="{D53C1EA8-9390-47F9-81D8-A7AD6413C13D}"/>
-    <hyperlink ref="D2" r:id="rId6" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EckQFKh7DbJBvlAvL8RH9-EBj63yTMh2IFRQU0-b-Ac9tg?e=dCk35z" xr:uid="{9BC5AD07-7EC4-4D2A-B1AE-FE6AFA2BA7AE}"/>
-    <hyperlink ref="D4" r:id="rId7" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EerP1pcja5VAkArC5lhHm0oBv7Dg-whvo3Dm3T8ebfzFrA?e=oFEzZs" xr:uid="{F6FDB76F-DA0D-4793-8EB7-EAB0AC807236}"/>
+    <hyperlink ref="D10" r:id="rId2" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
+    <hyperlink ref="D2" r:id="rId3" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EckQFKh7DbJBvlAvL8RH9-EBj63yTMh2IFRQU0-b-Ac9tg?e=dCk35z" xr:uid="{9BC5AD07-7EC4-4D2A-B1AE-FE6AFA2BA7AE}"/>
+    <hyperlink ref="D4" r:id="rId4" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EerP1pcja5VAkArC5lhHm0oBv7Dg-whvo3Dm3T8ebfzFrA?e=oFEzZs" xr:uid="{F6FDB76F-DA0D-4793-8EB7-EAB0AC807236}"/>
+    <hyperlink ref="D8" r:id="rId5" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/EhKjfsv8_RBPr6oodA_uZAoBHxT_wIrcXPru76Qkx65pRQ?e=afbBOD" xr:uid="{16D0E873-CD1F-42EA-A0BE-5F2E5E574857}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resource Links/Tech-Bootcamp-Links.xlsx
+++ b/Resource Links/Tech-Bootcamp-Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Resource Links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D77390-4543-4788-928B-E5E18CCC866C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C0658F-0876-4F92-A36F-23C8F594DE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,10 +80,10 @@
     <t>Recordings</t>
   </si>
   <si>
-    <t>Spring Boot  Recordings</t>
-  </si>
-  <si>
-    <t>Spring Core, REST and Data JPA Recordings</t>
+    <t>Spring Boot/React  Recordings</t>
+  </si>
+  <si>
+    <t>Spring Core, REST and Data JPA Recordings + ReactJS</t>
   </si>
 </sst>
 </file>
@@ -600,7 +600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>

--- a/Resource Links/Tech-Bootcamp-Links.xlsx
+++ b/Resource Links/Tech-Bootcamp-Links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Resource Links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C0658F-0876-4F92-A36F-23C8F594DE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9FEF29-0EDA-4B0D-8580-209953E6BC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Serial No.</t>
   </si>
@@ -80,10 +80,19 @@
     <t>Recordings</t>
   </si>
   <si>
-    <t>Spring Boot/React  Recordings</t>
-  </si>
-  <si>
-    <t>Spring Core, REST and Data JPA Recordings + ReactJS</t>
+    <t>Core Tech Recordings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spring Core, REST and Data JPA Recordings </t>
+  </si>
+  <si>
+    <t>Spring Boot  Recordings (Recordings till October 22nd,2025)</t>
+  </si>
+  <si>
+    <t>JavaScript(ES6), ReactJS Recordings</t>
+  </si>
+  <si>
+    <t>All current recordings</t>
   </si>
 </sst>
 </file>
@@ -131,27 +140,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -186,9 +180,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -604,35 +596,43 @@
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>14</v>
+      <c r="B8" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="D8" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="10"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -640,10 +640,11 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D6" r:id="rId1" xr:uid="{0C8BF935-1079-4255-9D07-C93C89C0D00D}"/>
-    <hyperlink ref="D10" r:id="rId2" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
+    <hyperlink ref="D12" r:id="rId2" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
     <hyperlink ref="D2" r:id="rId3" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EckQFKh7DbJBvlAvL8RH9-EBj63yTMh2IFRQU0-b-Ac9tg?e=dCk35z" xr:uid="{9BC5AD07-7EC4-4D2A-B1AE-FE6AFA2BA7AE}"/>
     <hyperlink ref="D4" r:id="rId4" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EerP1pcja5VAkArC5lhHm0oBv7Dg-whvo3Dm3T8ebfzFrA?e=oFEzZs" xr:uid="{F6FDB76F-DA0D-4793-8EB7-EAB0AC807236}"/>
-    <hyperlink ref="D8" r:id="rId5" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/EhKjfsv8_RBPr6oodA_uZAoBHxT_wIrcXPru76Qkx65pRQ?e=afbBOD" xr:uid="{16D0E873-CD1F-42EA-A0BE-5F2E5E574857}"/>
+    <hyperlink ref="D10" r:id="rId5" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/EhKjfsv8_RBPr6oodA_uZAoBHxT_wIrcXPru76Qkx65pRQ?e=afbBOD" xr:uid="{16D0E873-CD1F-42EA-A0BE-5F2E5E574857}"/>
+    <hyperlink ref="D8" r:id="rId6" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/IgDmrxUyB6a1RIZCIABGwukvAXigF8StP1XP4xD7QtdmOLI?e=acnhHD" xr:uid="{EC34F906-3729-4377-A749-E04D07566B6A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resource Links/Tech-Bootcamp-Links.xlsx
+++ b/Resource Links/Tech-Bootcamp-Links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Resource Links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9FEF29-0EDA-4B0D-8580-209953E6BC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D90E6E7-F7B5-4332-AE8B-7865C31FA803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Serial No.</t>
   </si>
@@ -93,6 +93,12 @@
   </si>
   <si>
     <t>All current recordings</t>
+  </si>
+  <si>
+    <t>React Training - Batch 2 - Consolidated Scores and Reports .xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">React Training - Batch 2 -  Consolidated Scores and Reports </t>
   </si>
 </sst>
 </file>
@@ -516,13 +522,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="43.42578125" customWidth="1"/>
     <col min="3" max="3" width="43.7109375" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" customWidth="1"/>
+    <col min="4" max="4" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -578,73 +584,93 @@
       <c r="C5" s="3"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>7</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="B14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D6" r:id="rId1" xr:uid="{0C8BF935-1079-4255-9D07-C93C89C0D00D}"/>
-    <hyperlink ref="D12" r:id="rId2" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
+    <hyperlink ref="D8" r:id="rId1" xr:uid="{0C8BF935-1079-4255-9D07-C93C89C0D00D}"/>
+    <hyperlink ref="D14" r:id="rId2" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
     <hyperlink ref="D2" r:id="rId3" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EckQFKh7DbJBvlAvL8RH9-EBj63yTMh2IFRQU0-b-Ac9tg?e=dCk35z" xr:uid="{9BC5AD07-7EC4-4D2A-B1AE-FE6AFA2BA7AE}"/>
     <hyperlink ref="D4" r:id="rId4" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EerP1pcja5VAkArC5lhHm0oBv7Dg-whvo3Dm3T8ebfzFrA?e=oFEzZs" xr:uid="{F6FDB76F-DA0D-4793-8EB7-EAB0AC807236}"/>
-    <hyperlink ref="D10" r:id="rId5" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/EhKjfsv8_RBPr6oodA_uZAoBHxT_wIrcXPru76Qkx65pRQ?e=afbBOD" xr:uid="{16D0E873-CD1F-42EA-A0BE-5F2E5E574857}"/>
-    <hyperlink ref="D8" r:id="rId6" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/IgDmrxUyB6a1RIZCIABGwukvAXigF8StP1XP4xD7QtdmOLI?e=acnhHD" xr:uid="{EC34F906-3729-4377-A749-E04D07566B6A}"/>
+    <hyperlink ref="D12" r:id="rId5" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/EhKjfsv8_RBPr6oodA_uZAoBHxT_wIrcXPru76Qkx65pRQ?e=afbBOD" xr:uid="{16D0E873-CD1F-42EA-A0BE-5F2E5E574857}"/>
+    <hyperlink ref="D10" r:id="rId6" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/IgDmrxUyB6a1RIZCIABGwukvAXigF8StP1XP4xD7QtdmOLI?e=acnhHD" xr:uid="{EC34F906-3729-4377-A749-E04D07566B6A}"/>
+    <hyperlink ref="D6" r:id="rId7" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/IQB4nf29hqPPQLKwwMZ1455AAdZappJNVShqaUY58KynhZ8?e=6NDKKe" xr:uid="{9EBA4E5B-E1F6-440F-9BEE-8E3066DF906F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resource Links/Tech-Bootcamp-Links.xlsx
+++ b/Resource Links/Tech-Bootcamp-Links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Resource Links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D90E6E7-F7B5-4332-AE8B-7865C31FA803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80761DC8-236E-412C-BAA9-AD484C5DFC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,9 +89,6 @@
     <t>Spring Boot  Recordings (Recordings till October 22nd,2025)</t>
   </si>
   <si>
-    <t>JavaScript(ES6), ReactJS Recordings</t>
-  </si>
-  <si>
     <t>All current recordings</t>
   </si>
   <si>
@@ -99,6 +96,9 @@
   </si>
   <si>
     <t xml:space="preserve">React Training - Batch 2 -  Consolidated Scores and Reports </t>
+  </si>
+  <si>
+    <t>JavaScript(ES6), ReactJS , Redux and Testing with Jest and RTL Recordings</t>
   </si>
 </sst>
 </file>
@@ -589,13 +589,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -631,15 +631,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>6</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>18</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>13</v>

--- a/Resource Links/Tech-Bootcamp-Links.xlsx
+++ b/Resource Links/Tech-Bootcamp-Links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Resource Links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80761DC8-236E-412C-BAA9-AD484C5DFC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10589C0-553B-41B6-9DF5-16C67A80BC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
   <si>
     <t>Serial No.</t>
   </si>
@@ -98,7 +98,13 @@
     <t xml:space="preserve">React Training - Batch 2 -  Consolidated Scores and Reports </t>
   </si>
   <si>
-    <t>JavaScript(ES6), ReactJS , Redux and Testing with Jest and RTL Recordings</t>
+    <t>Recording Topics</t>
+  </si>
+  <si>
+    <t>Description of Recordings</t>
+  </si>
+  <si>
+    <t>Brief description of Recordings</t>
   </si>
 </sst>
 </file>
@@ -522,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -635,8 +641,8 @@
       <c r="A12" s="1">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>20</v>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>17</v>
@@ -645,32 +651,51 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>7</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D8" r:id="rId1" xr:uid="{0C8BF935-1079-4255-9D07-C93C89C0D00D}"/>
-    <hyperlink ref="D14" r:id="rId2" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
+    <hyperlink ref="D16" r:id="rId2" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
     <hyperlink ref="D2" r:id="rId3" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EckQFKh7DbJBvlAvL8RH9-EBj63yTMh2IFRQU0-b-Ac9tg?e=dCk35z" xr:uid="{9BC5AD07-7EC4-4D2A-B1AE-FE6AFA2BA7AE}"/>
     <hyperlink ref="D4" r:id="rId4" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EerP1pcja5VAkArC5lhHm0oBv7Dg-whvo3Dm3T8ebfzFrA?e=oFEzZs" xr:uid="{F6FDB76F-DA0D-4793-8EB7-EAB0AC807236}"/>
     <hyperlink ref="D12" r:id="rId5" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/EhKjfsv8_RBPr6oodA_uZAoBHxT_wIrcXPru76Qkx65pRQ?e=afbBOD" xr:uid="{16D0E873-CD1F-42EA-A0BE-5F2E5E574857}"/>
     <hyperlink ref="D10" r:id="rId6" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/IgDmrxUyB6a1RIZCIABGwukvAXigF8StP1XP4xD7QtdmOLI?e=acnhHD" xr:uid="{EC34F906-3729-4377-A749-E04D07566B6A}"/>
     <hyperlink ref="D6" r:id="rId7" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/IQB4nf29hqPPQLKwwMZ1455AAdZappJNVShqaUY58KynhZ8?e=6NDKKe" xr:uid="{9EBA4E5B-E1F6-440F-9BEE-8E3066DF906F}"/>
+    <hyperlink ref="D14" r:id="rId8" xr:uid="{867DE2B9-2387-421B-A344-FD13F74FCCC9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resource Links/Tech-Bootcamp-Links.xlsx
+++ b/Resource Links/Tech-Bootcamp-Links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Resource Links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10589C0-553B-41B6-9DF5-16C67A80BC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8666702-C3F7-4DBA-AFEE-F83570E8C3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
   <si>
     <t>Serial No.</t>
   </si>
@@ -105,6 +105,15 @@
   </si>
   <si>
     <t>Brief description of Recordings</t>
+  </si>
+  <si>
+    <t>Assessment Scores</t>
+  </si>
+  <si>
+    <t>Assessment Scores - MCQs and ScreenShare Coding Tests</t>
+  </si>
+  <si>
+    <t>Assessment Scores-Tech Bootcamp</t>
   </si>
 </sst>
 </file>
@@ -683,8 +692,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>9</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -696,6 +716,7 @@
     <hyperlink ref="D10" r:id="rId6" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/IgDmrxUyB6a1RIZCIABGwukvAXigF8StP1XP4xD7QtdmOLI?e=acnhHD" xr:uid="{EC34F906-3729-4377-A749-E04D07566B6A}"/>
     <hyperlink ref="D6" r:id="rId7" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/IQB4nf29hqPPQLKwwMZ1455AAdZappJNVShqaUY58KynhZ8?e=6NDKKe" xr:uid="{9EBA4E5B-E1F6-440F-9BEE-8E3066DF906F}"/>
     <hyperlink ref="D14" r:id="rId8" xr:uid="{867DE2B9-2387-421B-A344-FD13F74FCCC9}"/>
+    <hyperlink ref="D18" r:id="rId9" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/IQCIhXcfdCeyS47Mn5kYTycRAdvRGcvsLc1DUzdmIVriG_4?e=UglLLF" xr:uid="{F48ECBF5-12B7-4CEA-A344-1F2C1EFDFA50}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Resource Links/Tech-Bootcamp-Links.xlsx
+++ b/Resource Links/Tech-Bootcamp-Links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Online Training\Apexon\GS-Training\Resource Links\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8666702-C3F7-4DBA-AFEE-F83570E8C3C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF18BA7-3338-4CB4-AD0D-CF537A427765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>Serial No.</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Batch 4 - Consolidated Scores and Reports.xlsx</t>
   </si>
   <si>
-    <t>Attendance/Assignment and Demos Status</t>
-  </si>
-  <si>
     <t>Recordings</t>
   </si>
   <si>
@@ -98,15 +95,6 @@
     <t xml:space="preserve">React Training - Batch 2 -  Consolidated Scores and Reports </t>
   </si>
   <si>
-    <t>Recording Topics</t>
-  </si>
-  <si>
-    <t>Description of Recordings</t>
-  </si>
-  <si>
-    <t>Brief description of Recordings</t>
-  </si>
-  <si>
     <t>Assessment Scores</t>
   </si>
   <si>
@@ -114,6 +102,21 @@
   </si>
   <si>
     <t>Assessment Scores-Tech Bootcamp</t>
+  </si>
+  <si>
+    <t>Tech Bootcamp-Core Tech-Batch 5-Consolidated Scores and Reports</t>
+  </si>
+  <si>
+    <t>Ongoing Training. Asessments and Demos Status + Recording Descriptions</t>
+  </si>
+  <si>
+    <t>Tech Bootcamp-Core Tech-Batch 5-Consolidated Scores and Reports.xlsx</t>
+  </si>
+  <si>
+    <t>Attendance/Assignment and Demos Status  + Recording Descriptions</t>
+  </si>
+  <si>
+    <t>All current recordings (.mp4 files)</t>
   </si>
 </sst>
 </file>
@@ -189,9 +192,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -201,7 +201,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -537,13 +542,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="43.42578125" customWidth="1"/>
     <col min="3" max="3" width="43.7109375" customWidth="1"/>
-    <col min="4" max="4" width="58.85546875" customWidth="1"/>
+    <col min="4" max="4" width="69.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -560,7 +565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -568,19 +573,19 @@
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="4"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="8"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -588,35 +593,35 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="9"/>
+      <c r="D5" s="8"/>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" s="4"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="9"/>
+      <c r="D7" s="8"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -628,7 +633,7 @@
       <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -636,14 +641,14 @@
       <c r="A10" s="1">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>14</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -651,72 +656,74 @@
         <v>6</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>7</v>
       </c>
-      <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
+      <c r="B14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="D15" s="10"/>
     </row>
     <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>8</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>8</v>
+        <v>19</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>9</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>25</v>
-      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D8" r:id="rId1" xr:uid="{0C8BF935-1079-4255-9D07-C93C89C0D00D}"/>
-    <hyperlink ref="D16" r:id="rId2" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
+    <hyperlink ref="D14" r:id="rId2" xr:uid="{B0689BD3-D1B4-45CD-BA2E-986B540DF4C9}"/>
     <hyperlink ref="D2" r:id="rId3" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EckQFKh7DbJBvlAvL8RH9-EBj63yTMh2IFRQU0-b-Ac9tg?e=dCk35z" xr:uid="{9BC5AD07-7EC4-4D2A-B1AE-FE6AFA2BA7AE}"/>
     <hyperlink ref="D4" r:id="rId4" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/EerP1pcja5VAkArC5lhHm0oBv7Dg-whvo3Dm3T8ebfzFrA?e=oFEzZs" xr:uid="{F6FDB76F-DA0D-4793-8EB7-EAB0AC807236}"/>
     <hyperlink ref="D12" r:id="rId5" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/EhKjfsv8_RBPr6oodA_uZAoBHxT_wIrcXPru76Qkx65pRQ?e=afbBOD" xr:uid="{16D0E873-CD1F-42EA-A0BE-5F2E5E574857}"/>
     <hyperlink ref="D10" r:id="rId6" display="https://isplahd-my.sharepoint.com/:f:/g/personal/stephen_samuels_apexon_com/IgDmrxUyB6a1RIZCIABGwukvAXigF8StP1XP4xD7QtdmOLI?e=acnhHD" xr:uid="{EC34F906-3729-4377-A749-E04D07566B6A}"/>
     <hyperlink ref="D6" r:id="rId7" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/IQB4nf29hqPPQLKwwMZ1455AAdZappJNVShqaUY58KynhZ8?e=6NDKKe" xr:uid="{9EBA4E5B-E1F6-440F-9BEE-8E3066DF906F}"/>
-    <hyperlink ref="D14" r:id="rId8" xr:uid="{867DE2B9-2387-421B-A344-FD13F74FCCC9}"/>
-    <hyperlink ref="D18" r:id="rId9" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/IQCIhXcfdCeyS47Mn5kYTycRAdvRGcvsLc1DUzdmIVriG_4?e=UglLLF" xr:uid="{F48ECBF5-12B7-4CEA-A344-1F2C1EFDFA50}"/>
+    <hyperlink ref="D16" r:id="rId8" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/IQCIhXcfdCeyS47Mn5kYTycRAdvRGcvsLc1DUzdmIVriG_4?e=UglLLF" xr:uid="{F48ECBF5-12B7-4CEA-A344-1F2C1EFDFA50}"/>
+    <hyperlink ref="D18" r:id="rId9" display="https://isplahd-my.sharepoint.com/:x:/g/personal/stephen_samuels_apexon_com/IQCOMOhBasGASIpp2cBAEw3bAdgIzdy4SlvljlldiqEncIk?e=ajSeQj" xr:uid="{3F78C9E4-6D65-4499-939D-2D369BAA7200}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
